--- a/delivery/levee_eval_api/excel_import/levee_import_k45500_demo.xlsx
+++ b/delivery/levee_eval_api/excel_import/levee_import_k45500_demo.xlsx
@@ -2504,7 +2504,7 @@
         <v>0.778</v>
       </c>
       <c r="L3" t="n">
-        <v>34.04</v>
+        <v>33.89</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
